--- a/Docs/Análise de requisitos - Foodverse.xlsx
+++ b/Docs/Análise de requisitos - Foodverse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/thiago_boliveira13_senacsp_edu_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84853EA7-A8FA-4930-9CB6-25537821DAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4108335E-3D65-43EB-8C67-C7849D19E41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E278343A-38FB-438C-A60B-2B741FA23712}"/>
   </bookViews>
@@ -5130,15 +5130,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="510c48d5-dbe4-4e17-a452-f7d17e07b1a2" xsi:nil="true"/>
@@ -5146,7 +5137,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100178FB635A72BD24F9593BACC8A54E00C" ma:contentTypeVersion="6" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="5f96df8db3a466a97af7346568c10bad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="510c48d5-dbe4-4e17-a452-f7d17e07b1a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2149f49d3bfd1a5194ee6db4c3062523" ns3:_="">
     <xsd:import namespace="510c48d5-dbe4-4e17-a452-f7d17e07b1a2"/>
@@ -5302,14 +5293,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62C86328-B636-4097-B813-7EEA87160C60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D1D167-336B-4DA5-93F1-338EAC446199}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D1D167-336B-4DA5-93F1-338EAC446199}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{167EE6BA-50DD-4E8D-B85E-07DFBB8CD311}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{167EE6BA-50DD-4E8D-B85E-07DFBB8CD311}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62C86328-B636-4097-B813-7EEA87160C60}"/>
 </file>